--- a/survey_templates/022_information_matrix_template_form--survey_templates.xlsx
+++ b/survey_templates/022_information_matrix_template_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>information_matrix_template_form</t>
+          <t>favorite_color</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Favorite color</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_2</t>
+          <t>favorite_animal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your favorite animal?</t>
+          <t>Favorite animal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_3</t>
+          <t>wake_up_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_4</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your age?</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_5</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is your email address?</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_6</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your phone number?</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_7</t>
+          <t>favorite_food</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is your note?</t>
+          <t>Favorite food</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_8</t>
+          <t>favorite_drink</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What date do you plan to start?</t>
+          <t>Favorite drink</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_9</t>
+          <t>favorite_hobby</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What time do you plan to start?</t>
+          <t>Favorite hobby</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_10</t>
+          <t>favorite_sport</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your name?</t>
+          <t>Favorite sport</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_11</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is your age?</t>
+          <t>What time do you plan to start?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12</t>
+          <t>favorite_genre</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your age group?</t>
+          <t>Favorite music genre</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_13</t>
+          <t>favorite_artist</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Favorite artist</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_14</t>
+          <t>favorite_social_media</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What time do you wake up?</t>
+          <t>Favorite social media</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_15</t>
+          <t>favorite_website</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is your favorite food?</t>
+          <t>Favorite website</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_16</t>
+          <t>favorite_color_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is your favorite drink?</t>
+          <t>Favorite color 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_17</t>
+          <t>favorite_food_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is your favorite hobby?</t>
+          <t>Favorite food 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_18</t>
+          <t>favorite_hobby_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is your favorite sport?</t>
+          <t>Favorite hobby 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_19</t>
+          <t>favorite_sport_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What time do you plan to finish?</t>
+          <t>Favorite sport 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_20</t>
+          <t>favorite_genre_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is your favorite music genre?</t>
+          <t>Favorite music genre 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>information_matrix_template_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your favorite artist?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>information_matrix_template_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your favorite social media?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>information_matrix_template_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is your favorite website?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>information_matrix_template_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your favorite color?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>information_matrix_template_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is your favorite food?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,1020 +1011,1190 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>red</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_2_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>green</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_2_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yellow</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>orange</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>purple</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_animal_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>cat</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_animal_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>dog</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_animal_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>elephant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>elephant</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_animal_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>lion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>lion</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_animal_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>bear</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_animal_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>rabbit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>pizza</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_12_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>burger</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_13_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>salad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_13_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>fruit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>fruit</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_13_choices</t>
+          <t>favorite_drink_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>water</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_13_choices</t>
+          <t>favorite_drink_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>juice</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_13_choices</t>
+          <t>favorite_drink_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>soda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>soda</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_13_choices</t>
+          <t>favorite_drink_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>tea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_15_choices</t>
+          <t>favorite_drink_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>coffee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_15_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>reading</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_15_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>gaming</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_15_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fruit</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fruit</t>
+          <t>hiking</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_16_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>swimming</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_16_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>juice</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>juice</t>
+          <t>dancing</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_16_choices</t>
+          <t>favorite_sport_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>soda</t>
+          <t>football</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>soda</t>
+          <t>football</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_16_choices</t>
+          <t>favorite_sport_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>basketball</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_16_choices</t>
+          <t>favorite_sport_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>coffee</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>coffee</t>
+          <t>tennis</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_17_choices</t>
+          <t>favorite_sport_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>baseball</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_17_choices</t>
+          <t>favorite_sport_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gaming</t>
+          <t>golf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gaming</t>
+          <t>golf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_17_choices</t>
+          <t>favorite_genre_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>rock</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_17_choices</t>
+          <t>favorite_genre_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>jazz</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_17_choices</t>
+          <t>favorite_genre_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dancing</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dancing</t>
+          <t>pop</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_18_choices</t>
+          <t>favorite_genre_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hip_hop</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hip hop</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_18_choices</t>
+          <t>favorite_genre_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>electronic</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_18_choices</t>
+          <t>favorite_artist_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>the_beatles</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>The Beatles</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_18_choices</t>
+          <t>favorite_artist_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>baseball</t>
+          <t>the_rolling_stones</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>baseball</t>
+          <t>The Rolling Stones</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_18_choices</t>
+          <t>favorite_artist_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>golf</t>
+          <t>taylor_swift</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>golf</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_20_choices</t>
+          <t>favorite_artist_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>kanye_west</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>Kanye West</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_20_choices</t>
+          <t>favorite_artist_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jazz</t>
+          <t>beyoncé</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jazz</t>
+          <t>Beyoncé</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_20_choices</t>
+          <t>favorite_social_media_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_20_choices</t>
+          <t>favorite_social_media_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>hip_hop</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>hip hop</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_20_choices</t>
+          <t>favorite_social_media_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_21_choices</t>
+          <t>favorite_social_media_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_21_choices</t>
+          <t>favorite_color_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>red</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_22_choices</t>
+          <t>favorite_color_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_22_choices</t>
+          <t>favorite_color_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>green</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_22_choices</t>
+          <t>favorite_color_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>yellow</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_22_choices</t>
+          <t>favorite_color_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>orange</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_24_choices</t>
+          <t>favorite_color_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>purple</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_24_choices</t>
+          <t>favorite_food_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>pizza</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_24_choices</t>
+          <t>favorite_food_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>burger</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_24_choices</t>
+          <t>favorite_food_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>salad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_24_choices</t>
+          <t>favorite_food_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>fruit</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>fruit</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_24_choices</t>
+          <t>favorite_hobby_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>reading</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_25_choices</t>
+          <t>favorite_hobby_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>gaming</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_25_choices</t>
+          <t>favorite_hobby_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>hiking</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_25_choices</t>
+          <t>favorite_hobby_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>swimming</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>information_matrix_template_form_25_choices</t>
+          <t>favorite_hobby_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>fruit</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>fruit</t>
+          <t>dancing</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>favorite_sport_2_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>favorite_sport_2_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>favorite_sport_2_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>favorite_sport_2_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>baseball</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>baseball</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>favorite_sport_2_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>golf</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>golf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>favorite_genre_2_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>favorite_genre_2_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>jazz</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jazz</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>favorite_genre_2_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>favorite_genre_2_choices</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>hip_hop</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>hip hop</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>favorite_genre_2_choices</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>electronic</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>electronic</t>
         </is>
       </c>
     </row>
